--- a/artfynd/A 2898-2026 artfynd.xlsx
+++ b/artfynd/A 2898-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130057089</v>
       </c>
       <c r="B2" t="n">
-        <v>97166</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -760,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130057096</v>
+        <v>130057111</v>
       </c>
       <c r="B3" t="n">
-        <v>91692</v>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402393</v>
+        <v>402207</v>
       </c>
       <c r="R3" t="n">
-        <v>6706564</v>
+        <v>6706447</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,15 +857,112 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130057096</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Marrbäckmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>402393</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6706564</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2898-2026 artfynd.xlsx
+++ b/artfynd/A 2898-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130057089</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130057111</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130057096</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>